--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2020_magallanes.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:14</t>
+    <t xml:space="preserve">2026-09-24 01:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -650,17 +650,21 @@
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="n">
+        <v>0.72</v>
+      </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
@@ -669,17 +673,21 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="n">
+        <v>0.81</v>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="G9" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -688,17 +696,21 @@
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="n">
+        <v>0.09</v>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>-0.12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
@@ -707,17 +719,21 @@
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>334</v>
-      </c>
-      <c r="G11" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>-0.46</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
@@ -749,17 +765,21 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="n">
+        <v>-0.93</v>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>-0.93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
@@ -768,17 +788,21 @@
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1.24</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
@@ -787,17 +811,21 @@
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="n">
+        <v>-0.46</v>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="G15" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>-0.65</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
